--- a/HPO_1D_energies.xlsx
+++ b/HPO_1D_energies.xlsx
@@ -4999,6 +4999,10 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>

--- a/HPO_1D_energies.xlsx
+++ b/HPO_1D_energies.xlsx
@@ -11720,6 +11720,7 @@
     <sortCondition ref="E1:E376"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
